--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120463088</v>
+        <v>120462876</v>
       </c>
       <c r="B3" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711997</v>
+        <v>711992</v>
       </c>
       <c r="R3" t="n">
-        <v>6664596</v>
+        <v>6664606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,26 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120462876</v>
+        <v>120463088</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711992</v>
+        <v>711997</v>
       </c>
       <c r="R4" t="n">
-        <v>6664606</v>
+        <v>6664596</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,6 +983,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120463177</v>
+        <v>120463088</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712021</v>
+        <v>711997</v>
       </c>
       <c r="R2" t="n">
-        <v>6664589</v>
+        <v>6664596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120462876</v>
+        <v>120462987</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711992</v>
+        <v>712007</v>
       </c>
       <c r="R3" t="n">
-        <v>6664606</v>
+        <v>6664604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120463088</v>
+        <v>120462876</v>
       </c>
       <c r="B4" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +920,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711997</v>
+        <v>711992</v>
       </c>
       <c r="R4" t="n">
-        <v>6664596</v>
+        <v>6664606</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,26 +1003,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120462987</v>
+        <v>120463177</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712007</v>
+        <v>712021</v>
       </c>
       <c r="R5" t="n">
-        <v>6664604</v>
+        <v>6664589</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,2444 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120513486</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>712110</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6664573</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120513619</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74593</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>712104</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6664480</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120511990</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>712171</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6664553</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120512307</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>712227</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6664593</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120511591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>712148</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6664489</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120513031</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>712050</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6664685</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120513702</v>
+      </c>
+      <c r="B12" t="n">
+        <v>74593</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>712121</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6664450</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120511847</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>712148</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6664547</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120512601</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78568</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>712150</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6664600</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120513525</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74593</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>712111</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6664536</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120511625</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78568</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>712146</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6664502</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120513020</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110061</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>712049</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6664686</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120512202</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>712195</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6664563</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120512718</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>712105</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6664637</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120514238</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>712121</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6664413</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120513457</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105032</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>712093</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6664550</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120512543</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>712164</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6664591</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120512615</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>712151</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6664605</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120511696</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>712154</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6664523</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120511513</v>
+      </c>
+      <c r="B25" t="n">
+        <v>74593</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>712153</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6664489</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120512608</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>712147</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6664601</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120512798</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>712089</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6664619</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120513162</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>712034</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6664626</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120463088</v>
+        <v>120462987</v>
       </c>
       <c r="B2" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711997</v>
+        <v>712007</v>
       </c>
       <c r="R2" t="n">
-        <v>6664596</v>
+        <v>6664604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,26 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120462987</v>
+        <v>120463177</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -832,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712007</v>
+        <v>712021</v>
       </c>
       <c r="R3" t="n">
-        <v>6664604</v>
+        <v>6664589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120462876</v>
+        <v>120463088</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711992</v>
+        <v>711997</v>
       </c>
       <c r="R4" t="n">
-        <v>6664606</v>
+        <v>6664596</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,6 +983,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120463177</v>
+        <v>120462876</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712021</v>
+        <v>711992</v>
       </c>
       <c r="R5" t="n">
-        <v>6664589</v>
+        <v>6664606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120513486</v>
+        <v>120511513</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>74593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,38 +1142,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712110</v>
+        <v>712153</v>
       </c>
       <c r="R6" t="n">
-        <v>6664573</v>
+        <v>6664489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,6 +1216,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1232,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120513619</v>
+        <v>120513486</v>
       </c>
       <c r="B7" t="n">
-        <v>74593</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,38 +1264,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712104</v>
+        <v>712110</v>
       </c>
       <c r="R7" t="n">
-        <v>6664480</v>
+        <v>6664573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120511990</v>
+        <v>120513702</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>74593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,25 +1366,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712171</v>
+        <v>712121</v>
       </c>
       <c r="R8" t="n">
-        <v>6664553</v>
+        <v>6664450</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120512307</v>
+        <v>120511990</v>
       </c>
       <c r="B9" t="n">
-        <v>95478</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712227</v>
+        <v>712171</v>
       </c>
       <c r="R9" t="n">
-        <v>6664593</v>
+        <v>6664553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,26 +1542,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120511591</v>
+        <v>120513162</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1603,14 +1603,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712148</v>
+        <v>712034</v>
       </c>
       <c r="R10" t="n">
-        <v>6664489</v>
+        <v>6664626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120513031</v>
+        <v>120513457</v>
       </c>
       <c r="B11" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,21 +1685,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712050</v>
+        <v>712093</v>
       </c>
       <c r="R11" t="n">
-        <v>6664685</v>
+        <v>6664550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120513702</v>
+        <v>120513031</v>
       </c>
       <c r="B12" t="n">
-        <v>74593</v>
+        <v>100194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,34 +1787,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712121</v>
+        <v>712050</v>
       </c>
       <c r="R12" t="n">
-        <v>6664450</v>
+        <v>6664685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120512601</v>
+        <v>120512202</v>
       </c>
       <c r="B14" t="n">
-        <v>78568</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,38 +1987,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712150</v>
+        <v>712195</v>
       </c>
       <c r="R14" t="n">
-        <v>6664600</v>
+        <v>6664563</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120513525</v>
+        <v>120512307</v>
       </c>
       <c r="B15" t="n">
-        <v>74593</v>
+        <v>95478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,38 +2098,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712111</v>
+        <v>712227</v>
       </c>
       <c r="R15" t="n">
-        <v>6664536</v>
+        <v>6664593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,6 +2172,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2179,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120511625</v>
+        <v>120513619</v>
       </c>
       <c r="B16" t="n">
-        <v>78568</v>
+        <v>74593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2224,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712146</v>
+        <v>712104</v>
       </c>
       <c r="R16" t="n">
-        <v>6664502</v>
+        <v>6664480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120513020</v>
+        <v>120512798</v>
       </c>
       <c r="B17" t="n">
-        <v>110061</v>
+        <v>91881</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,25 +2322,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2321,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712049</v>
+        <v>712089</v>
       </c>
       <c r="R17" t="n">
-        <v>6664686</v>
+        <v>6664619</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120512202</v>
+        <v>120512718</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,47 +2424,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712195</v>
+        <v>712105</v>
       </c>
       <c r="R18" t="n">
-        <v>6664563</v>
+        <v>6664637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,6 +2498,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2494,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120512718</v>
+        <v>120511625</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>78568</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2506,38 +2546,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712105</v>
+        <v>712146</v>
       </c>
       <c r="R19" t="n">
-        <v>6664637</v>
+        <v>6664502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,26 +2620,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2616,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120514238</v>
+        <v>120511591</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2628,38 +2648,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712121</v>
+        <v>712148</v>
       </c>
       <c r="R20" t="n">
-        <v>6664413</v>
+        <v>6664489</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2747,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120513457</v>
+        <v>120513020</v>
       </c>
       <c r="B21" t="n">
-        <v>105032</v>
+        <v>110061</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,21 +2763,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2787,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712093</v>
+        <v>712049</v>
       </c>
       <c r="R21" t="n">
-        <v>6664550</v>
+        <v>6664686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120512543</v>
+        <v>120512608</v>
       </c>
       <c r="B22" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2865,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712164</v>
+        <v>712147</v>
       </c>
       <c r="R22" t="n">
-        <v>6664591</v>
+        <v>6664601</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,10 +2951,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120512615</v>
+        <v>120514238</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>100194</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,34 +2967,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712151</v>
+        <v>712121</v>
       </c>
       <c r="R23" t="n">
-        <v>6664605</v>
+        <v>6664413</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120511696</v>
+        <v>120512601</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78568</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3036,43 +3065,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712154</v>
+        <v>712150</v>
       </c>
       <c r="R24" t="n">
-        <v>6664523</v>
+        <v>6664600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120511513</v>
+        <v>120512543</v>
       </c>
       <c r="B25" t="n">
-        <v>74593</v>
+        <v>90600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3143,38 +3167,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712153</v>
+        <v>712164</v>
       </c>
       <c r="R25" t="n">
-        <v>6664489</v>
+        <v>6664591</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,26 +3241,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3253,10 +3257,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120512608</v>
+        <v>120512615</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3265,25 +3269,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712147</v>
+        <v>712151</v>
       </c>
       <c r="R26" t="n">
-        <v>6664601</v>
+        <v>6664605</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3355,10 +3359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120512798</v>
+        <v>120511696</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3371,34 +3375,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712089</v>
+        <v>712154</v>
       </c>
       <c r="R27" t="n">
-        <v>6664619</v>
+        <v>6664523</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120513162</v>
+        <v>120513525</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3469,47 +3478,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712034</v>
+        <v>712111</v>
       </c>
       <c r="R28" t="n">
-        <v>6664626</v>
+        <v>6664536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120462987</v>
+        <v>120463177</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712007</v>
+        <v>712021</v>
       </c>
       <c r="R2" t="n">
-        <v>6664604</v>
+        <v>6664589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120463177</v>
+        <v>120462876</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712021</v>
+        <v>711992</v>
       </c>
       <c r="R3" t="n">
-        <v>6664589</v>
+        <v>6664606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120463088</v>
+        <v>120462987</v>
       </c>
       <c r="B4" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711997</v>
+        <v>712007</v>
       </c>
       <c r="R4" t="n">
-        <v>6664596</v>
+        <v>6664604</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,26 +992,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120462876</v>
+        <v>120463088</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,47 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711992</v>
+        <v>711997</v>
       </c>
       <c r="R5" t="n">
-        <v>6664606</v>
+        <v>6664596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,6 +1094,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120511513</v>
+        <v>120513525</v>
       </c>
       <c r="B6" t="n">
         <v>74593</v>
@@ -1166,14 +1166,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712153</v>
+        <v>712111</v>
       </c>
       <c r="R6" t="n">
-        <v>6664489</v>
+        <v>6664536</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,26 +1216,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1252,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120513486</v>
+        <v>120511513</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>74593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,38 +1244,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712110</v>
+        <v>712153</v>
       </c>
       <c r="R7" t="n">
-        <v>6664573</v>
+        <v>6664489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,6 +1318,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120513702</v>
+        <v>120512543</v>
       </c>
       <c r="B8" t="n">
-        <v>74593</v>
+        <v>90600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,38 +1366,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712121</v>
+        <v>712164</v>
       </c>
       <c r="R8" t="n">
-        <v>6664450</v>
+        <v>6664591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120511990</v>
+        <v>120513162</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,38 +1468,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712171</v>
+        <v>712034</v>
       </c>
       <c r="R9" t="n">
-        <v>6664553</v>
+        <v>6664626</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120513162</v>
+        <v>120514238</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,47 +1579,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712034</v>
+        <v>712121</v>
       </c>
       <c r="R10" t="n">
-        <v>6664626</v>
+        <v>6664413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120513457</v>
+        <v>120511990</v>
       </c>
       <c r="B11" t="n">
-        <v>105032</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,38 +1681,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712093</v>
+        <v>712171</v>
       </c>
       <c r="R11" t="n">
-        <v>6664550</v>
+        <v>6664553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120513031</v>
+        <v>120513619</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>74593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,34 +1787,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712050</v>
+        <v>712104</v>
       </c>
       <c r="R12" t="n">
-        <v>6664685</v>
+        <v>6664480</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120511847</v>
+        <v>120511625</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>78568</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,25 +1885,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712148</v>
+        <v>712146</v>
       </c>
       <c r="R13" t="n">
-        <v>6664547</v>
+        <v>6664502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120513619</v>
+        <v>120512718</v>
       </c>
       <c r="B16" t="n">
-        <v>74593</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,38 +2220,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712104</v>
+        <v>712105</v>
       </c>
       <c r="R16" t="n">
-        <v>6664480</v>
+        <v>6664637</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,6 +2294,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2310,7 +2330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120512798</v>
+        <v>120512608</v>
       </c>
       <c r="B17" t="n">
         <v>91881</v>
@@ -2350,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712089</v>
+        <v>712147</v>
       </c>
       <c r="R17" t="n">
-        <v>6664619</v>
+        <v>6664601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120512718</v>
+        <v>120511847</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,34 +2448,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712105</v>
+        <v>712148</v>
       </c>
       <c r="R18" t="n">
-        <v>6664637</v>
+        <v>6664547</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,26 +2518,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120511625</v>
+        <v>120513486</v>
       </c>
       <c r="B19" t="n">
-        <v>78568</v>
+        <v>90600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,38 +2546,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712146</v>
+        <v>712110</v>
       </c>
       <c r="R19" t="n">
-        <v>6664502</v>
+        <v>6664573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120511591</v>
+        <v>120513457</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,47 +2648,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712148</v>
+        <v>712093</v>
       </c>
       <c r="R20" t="n">
-        <v>6664489</v>
+        <v>6664550</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120513020</v>
+        <v>120512601</v>
       </c>
       <c r="B21" t="n">
-        <v>110061</v>
+        <v>78568</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2787,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712049</v>
+        <v>712150</v>
       </c>
       <c r="R21" t="n">
-        <v>6664686</v>
+        <v>6664600</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2849,10 +2840,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120512608</v>
+        <v>120511696</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2865,34 +2856,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712147</v>
+        <v>712154</v>
       </c>
       <c r="R22" t="n">
-        <v>6664601</v>
+        <v>6664523</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2951,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120514238</v>
+        <v>120512798</v>
       </c>
       <c r="B23" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2963,38 +2959,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712121</v>
+        <v>712089</v>
       </c>
       <c r="R23" t="n">
-        <v>6664413</v>
+        <v>6664619</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3053,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120512601</v>
+        <v>120511591</v>
       </c>
       <c r="B24" t="n">
-        <v>78568</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3065,38 +3061,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712150</v>
+        <v>712148</v>
       </c>
       <c r="R24" t="n">
-        <v>6664600</v>
+        <v>6664489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120512543</v>
+        <v>120512615</v>
       </c>
       <c r="B25" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,25 +3172,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3195,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712164</v>
+        <v>712151</v>
       </c>
       <c r="R25" t="n">
-        <v>6664591</v>
+        <v>6664605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120512615</v>
+        <v>120513031</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3273,21 +3278,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712151</v>
+        <v>712050</v>
       </c>
       <c r="R26" t="n">
-        <v>6664605</v>
+        <v>6664685</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120511696</v>
+        <v>120513702</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>74593</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3371,43 +3376,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712154</v>
+        <v>712121</v>
       </c>
       <c r="R27" t="n">
-        <v>6664523</v>
+        <v>6664450</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120513525</v>
+        <v>120513020</v>
       </c>
       <c r="B28" t="n">
-        <v>74593</v>
+        <v>110061</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712111</v>
+        <v>712049</v>
       </c>
       <c r="R28" t="n">
-        <v>6664536</v>
+        <v>6664686</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -3364,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120513702</v>
+        <v>120513020</v>
       </c>
       <c r="B27" t="n">
-        <v>74593</v>
+        <v>110061</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3380,34 +3380,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>219711</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
+          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712121</v>
+        <v>712049</v>
       </c>
       <c r="R27" t="n">
-        <v>6664450</v>
+        <v>6664686</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120513020</v>
+        <v>120513702</v>
       </c>
       <c r="B28" t="n">
-        <v>110061</v>
+        <v>74593</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,34 +3482,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tullviksbäcken, Tullviksbäcken, Upl</t>
+          <t>Norra Fjällboholmarna, Norra Fjällboholmarna, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712049</v>
+        <v>712121</v>
       </c>
       <c r="R28" t="n">
-        <v>6664686</v>
+        <v>6664450</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>120511696</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>120511696</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>120511696</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>120511696</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 44237-2024 artfynd.xlsx
+++ b/artfynd/A 44237-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>120511696</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>121326360</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
